--- a/pedidos/PAV2026013S.xlsx
+++ b/pedidos/PAV2026013S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Agroserver\gestao_projetos\08_Processo_Químico\02_Clientes\OS_2026\ATVOS\OS_013\PAV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/pedidos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEB7480-D70E-4B7C-A47C-02F1FEA7FDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DAEB7480-D70E-4B7C-A47C-02F1FEA7FDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB4B3D07-7A41-4B38-A376-8DA0EE07C5EC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUST6_LIBSrest" sheetId="1" r:id="rId1"/>
@@ -1013,6 +1013,68 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
